--- a/checklist_forms/039_cottage_safety_inspection_checklist--checklist_forms.xlsx
+++ b/checklist_forms/039_cottage_safety_inspection_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_issues_with_electrical',_'value':_'no_issues_with_electrical'}</t>
+          <t>no_issues_with_electrical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No issues with electrical', 'value': 'No issues with electrical'}</t>
+          <t>No issues with electrical</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'some_issues_with_electrical',_'value':_'some_issues_with_electrical'}</t>
+          <t>some_issues_with_electrical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Some issues with electrical', 'value': 'Some issues with electrical'}</t>
+          <t>Some issues with electrical</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'major_electrical_issues',_'value':_'major_electrical_issues'}</t>
+          <t>major_electrical_issues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Major electrical issues', 'value': 'Major electrical issues'}</t>
+          <t>Major electrical issues</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_issues_with_plumbing',_'value':_'no_issues_with_plumbing'}</t>
+          <t>no_issues_with_plumbing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No issues with plumbing', 'value': 'No issues with plumbing'}</t>
+          <t>No issues with plumbing</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'some_issues_with_plumbing',_'value':_'some_issues_with_plumbing'}</t>
+          <t>some_issues_with_plumbing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Some issues with plumbing', 'value': 'Some issues with plumbing'}</t>
+          <t>Some issues with plumbing</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'major_plumbing_issues',_'value':_'major_plumbing_issues'}</t>
+          <t>major_plumbing_issues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Major plumbing issues', 'value': 'Major plumbing issues'}</t>
+          <t>Major plumbing issues</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_issues_with_fire_safety',_'value':_'no_issues_with_fire_safety'}</t>
+          <t>no_issues_with_fire_safety</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No issues with fire safety', 'value': 'No issues with fire safety'}</t>
+          <t>No issues with fire safety</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'some_issues_with_fire_safety',_'value':_'some_issues_with_fire_safety'}</t>
+          <t>some_issues_with_fire_safety</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Some issues with fire safety', 'value': 'Some issues with fire safety'}</t>
+          <t>Some issues with fire safety</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'major_fire_safety_issues',_'value':_'major_fire_safety_issues'}</t>
+          <t>major_fire_safety_issues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Major fire safety issues', 'value': 'Major fire safety issues'}</t>
+          <t>Major fire safety issues</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'no_issues_with_heating/cooling',_'value':_'no_issues_with_heating/cooling'}</t>
+          <t>no_issues_with_heating/cooling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'No issues with heating/cooling', 'value': 'No issues with heating/cooling'}</t>
+          <t>No issues with heating/cooling</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'some_issues_with_heating/cooling',_'value':_'some_issues_with_heating/cooling'}</t>
+          <t>some_issues_with_heating/cooling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Some issues with heating/cooling', 'value': 'Some issues with heating/cooling'}</t>
+          <t>Some issues with heating/cooling</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'major_heating/cooling_issues',_'value':_'major_heating/cooling_issues'}</t>
+          <t>major_heating/cooling_issues</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Major heating/cooling issues', 'value': 'Major heating/cooling issues'}</t>
+          <t>Major heating/cooling issues</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Yes', 'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'No', 'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
